--- a/figures/Figure 10/Gain_200K_synthetic.xlsx
+++ b/figures/Figure 10/Gain_200K_synthetic.xlsx
@@ -5,15 +5,15 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\prata\Files\Git\Causal-Search-for-Skylines\graphs\Figure 10\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\prata\Files\Git\Causal-Search-for-Skylines\figures\Figure 10\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1DCBF4B5-13AA-4D34-AA1E-D87535097F9A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E59FE0FC-B105-4902-A6EE-91BE2345CEA8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="16776" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="15675" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Gain" sheetId="1" r:id="rId1"/>
+    <sheet name="Summary" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -1490,7 +1490,7 @@
           <c:order val="0"/>
           <c:tx>
             <c:strRef>
-              <c:f>Gain!$E$382</c:f>
+              <c:f>Summary!$E$382</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -1861,11 +1861,11 @@
               <c:extLst>
                 <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
                   <c15:fullRef>
-                    <c15:sqref>Gain!$F$381:$K$381</c15:sqref>
+                    <c15:sqref>Summary!$F$381:$K$381</c15:sqref>
                   </c15:fullRef>
                 </c:ext>
               </c:extLst>
-              <c:f>(Gain!$F$381:$G$381,Gain!$K$381)</c:f>
+              <c:f>(Summary!$F$381:$G$381,Summary!$K$381)</c:f>
               <c:strCache>
                 <c:ptCount val="3"/>
                 <c:pt idx="0">
@@ -1885,11 +1885,11 @@
               <c:extLst>
                 <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
                   <c15:fullRef>
-                    <c15:sqref>Gain!$F$382:$K$382</c15:sqref>
+                    <c15:sqref>Summary!$F$382:$K$382</c15:sqref>
                   </c15:fullRef>
                 </c:ext>
               </c:extLst>
-              <c:f>(Gain!$F$382:$G$382,Gain!$K$382)</c:f>
+              <c:f>(Summary!$F$382:$G$382,Summary!$K$382)</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="3"/>
@@ -3299,13 +3299,13 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:K383"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="7" width="10" customWidth="1"/>
     <col min="8" max="11" width="20" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:11" x14ac:dyDescent="0.45">
       <c r="F1" s="7" t="s">
         <v>0</v>
       </c>
@@ -3315,7 +3315,7 @@
       <c r="J1" s="8"/>
       <c r="K1" s="8"/>
     </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:11" x14ac:dyDescent="0.45">
       <c r="E2" s="5" t="s">
         <v>386</v>
       </c>
@@ -3338,7 +3338,7 @@
         <v>393</v>
       </c>
     </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A3">
         <v>16</v>
       </c>
@@ -3373,7 +3373,7 @@
         <v>0.13687912500172389</v>
       </c>
     </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A4">
         <v>16</v>
       </c>
@@ -3408,7 +3408,7 @@
         <v>0.13672664260084269</v>
       </c>
     </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A5">
         <v>16</v>
       </c>
@@ -3443,7 +3443,7 @@
         <v>0.1344424359980621</v>
       </c>
     </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A6">
         <v>16</v>
       </c>
@@ -3478,7 +3478,7 @@
         <v>0.14385242019925501</v>
       </c>
     </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A7">
         <v>16</v>
       </c>
@@ -3513,7 +3513,7 @@
         <v>0.14495635519851929</v>
       </c>
     </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A8">
         <v>16</v>
       </c>
@@ -3548,7 +3548,7 @@
         <v>0.13692403980094239</v>
       </c>
     </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A9">
         <v>16</v>
       </c>
@@ -3583,7 +3583,7 @@
         <v>0.13987677120167061</v>
       </c>
     </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A10">
         <v>16</v>
       </c>
@@ -3618,7 +3618,7 @@
         <v>0.1462952795991441</v>
       </c>
     </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A11">
         <v>16</v>
       </c>
@@ -3653,7 +3653,7 @@
         <v>0.15268465380067939</v>
       </c>
     </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A12">
         <v>16</v>
       </c>
@@ -3688,7 +3688,7 @@
         <v>0.13015695159847379</v>
       </c>
     </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A13">
         <v>16</v>
       </c>
@@ -3723,7 +3723,7 @@
         <v>0.13997591600054879</v>
       </c>
     </row>
-    <row r="14" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A14">
         <v>16</v>
       </c>
@@ -3758,7 +3758,7 @@
         <v>0.14514394239959069</v>
       </c>
     </row>
-    <row r="15" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A15">
         <v>16</v>
       </c>
@@ -3793,7 +3793,7 @@
         <v>0.14640228679927531</v>
       </c>
     </row>
-    <row r="16" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A16">
         <v>16</v>
       </c>
@@ -3828,7 +3828,7 @@
         <v>0.142597576600383</v>
       </c>
     </row>
-    <row r="17" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A17">
         <v>16</v>
       </c>
@@ -3863,7 +3863,7 @@
         <v>0.1417558996006846</v>
       </c>
     </row>
-    <row r="18" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A18">
         <v>16</v>
       </c>
@@ -3898,7 +3898,7 @@
         <v>0.15184278639935661</v>
       </c>
     </row>
-    <row r="19" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A19">
         <v>16</v>
       </c>
@@ -3933,7 +3933,7 @@
         <v>0.1268688144016778</v>
       </c>
     </row>
-    <row r="20" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A20">
         <v>16</v>
       </c>
@@ -3968,7 +3968,7 @@
         <v>0.12897388379933539</v>
       </c>
     </row>
-    <row r="21" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A21">
         <v>16</v>
       </c>
@@ -4003,7 +4003,7 @@
         <v>0.1490068903993233</v>
       </c>
     </row>
-    <row r="22" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A22">
         <v>16</v>
       </c>
@@ -4038,7 +4038,7 @@
         <v>0.13608688120002629</v>
       </c>
     </row>
-    <row r="23" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A23">
         <v>16</v>
       </c>
@@ -4073,7 +4073,7 @@
         <v>0.1465954259998398</v>
       </c>
     </row>
-    <row r="24" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A24">
         <v>16</v>
       </c>
@@ -4108,7 +4108,7 @@
         <v>0.1333187347991043</v>
       </c>
     </row>
-    <row r="25" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A25">
         <v>16</v>
       </c>
@@ -4143,7 +4143,7 @@
         <v>0.1433540390004055</v>
       </c>
     </row>
-    <row r="26" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A26">
         <v>16</v>
       </c>
@@ -4178,7 +4178,7 @@
         <v>0.14789283539867029</v>
       </c>
     </row>
-    <row r="27" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A27">
         <v>16</v>
       </c>
@@ -4213,7 +4213,7 @@
         <v>0.14066022820043139</v>
       </c>
     </row>
-    <row r="28" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A28">
         <v>16</v>
       </c>
@@ -4248,7 +4248,7 @@
         <v>0.1388592783972854</v>
       </c>
     </row>
-    <row r="29" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A29">
         <v>16</v>
       </c>
@@ -4283,7 +4283,7 @@
         <v>0.14233221199974649</v>
       </c>
     </row>
-    <row r="30" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A30">
         <v>16</v>
       </c>
@@ -4318,7 +4318,7 @@
         <v>0.13731448680046021</v>
       </c>
     </row>
-    <row r="31" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A31">
         <v>16</v>
       </c>
@@ -4353,7 +4353,7 @@
         <v>0.14667340380110541</v>
       </c>
     </row>
-    <row r="32" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A32">
         <v>16</v>
       </c>
@@ -4388,7 +4388,7 @@
         <v>0.13182079640100711</v>
       </c>
     </row>
-    <row r="33" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A33">
         <v>16</v>
       </c>
@@ -4423,7 +4423,7 @@
         <v>0.1331598148011835</v>
       </c>
     </row>
-    <row r="34" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A34">
         <v>16</v>
       </c>
@@ -4458,7 +4458,7 @@
         <v>0.13836477539880429</v>
       </c>
     </row>
-    <row r="35" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A35">
         <v>16</v>
       </c>
@@ -4493,7 +4493,7 @@
         <v>0.13841787279961859</v>
       </c>
     </row>
-    <row r="36" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A36">
         <v>16</v>
       </c>
@@ -4528,7 +4528,7 @@
         <v>0.13444849740044451</v>
       </c>
     </row>
-    <row r="37" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A37">
         <v>16</v>
       </c>
@@ -4563,7 +4563,7 @@
         <v>0.1482975557984901</v>
       </c>
     </row>
-    <row r="38" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A38">
         <v>16</v>
       </c>
@@ -4598,7 +4598,7 @@
         <v>0.1354882329978864</v>
       </c>
     </row>
-    <row r="39" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A39">
         <v>16</v>
       </c>
@@ -4633,7 +4633,7 @@
         <v>0.13488352880085591</v>
       </c>
     </row>
-    <row r="40" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A40">
         <v>16</v>
       </c>
@@ -4668,7 +4668,7 @@
         <v>0.14299506020033731</v>
       </c>
     </row>
-    <row r="41" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A41">
         <v>16</v>
       </c>
@@ -4703,7 +4703,7 @@
         <v>0.15196651660226049</v>
       </c>
     </row>
-    <row r="42" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A42">
         <v>16</v>
       </c>
@@ -4738,7 +4738,7 @@
         <v>0.1476047567979549</v>
       </c>
     </row>
-    <row r="43" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A43">
         <v>16</v>
       </c>
@@ -4773,7 +4773,7 @@
         <v>0.14183328320068539</v>
       </c>
     </row>
-    <row r="44" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A44">
         <v>16</v>
       </c>
@@ -4808,7 +4808,7 @@
         <v>0.1384287362001487</v>
       </c>
     </row>
-    <row r="45" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A45">
         <v>16</v>
       </c>
@@ -4843,7 +4843,7 @@
         <v>0.13911368920089451</v>
       </c>
     </row>
-    <row r="46" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A46">
         <v>16</v>
       </c>
@@ -4878,7 +4878,7 @@
         <v>0.14797769279830389</v>
       </c>
     </row>
-    <row r="47" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A47">
         <v>16</v>
       </c>
@@ -4913,7 +4913,7 @@
         <v>0.14206179699976931</v>
       </c>
     </row>
-    <row r="48" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A48">
         <v>16</v>
       </c>
@@ -4948,7 +4948,7 @@
         <v>0.1424313545998302</v>
       </c>
     </row>
-    <row r="49" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A49">
         <v>16</v>
       </c>
@@ -4983,7 +4983,7 @@
         <v>0.15068343559978531</v>
       </c>
     </row>
-    <row r="50" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A50">
         <v>16</v>
       </c>
@@ -5018,7 +5018,7 @@
         <v>0.140692534801201</v>
       </c>
     </row>
-    <row r="51" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A51">
         <v>16</v>
       </c>
@@ -5053,7 +5053,7 @@
         <v>0.14807126419909761</v>
       </c>
     </row>
-    <row r="52" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A52">
         <v>16</v>
       </c>
@@ -5088,7 +5088,7 @@
         <v>0.1249505617990508</v>
       </c>
     </row>
-    <row r="53" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A53">
         <v>16</v>
       </c>
@@ -5123,7 +5123,7 @@
         <v>0.13574395679752341</v>
       </c>
     </row>
-    <row r="54" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A54">
         <v>16</v>
       </c>
@@ -5158,7 +5158,7 @@
         <v>0.1400946905996534</v>
       </c>
     </row>
-    <row r="55" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A55">
         <v>16</v>
       </c>
@@ -5193,7 +5193,7 @@
         <v>0.1359037944013835</v>
       </c>
     </row>
-    <row r="56" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A56">
         <v>16</v>
       </c>
@@ -5228,7 +5228,7 @@
         <v>0.1408531164008309</v>
       </c>
     </row>
-    <row r="57" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A57">
         <v>16</v>
       </c>
@@ -5263,7 +5263,7 @@
         <v>0.13583635040267841</v>
       </c>
     </row>
-    <row r="58" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A58">
         <v>16</v>
       </c>
@@ -5298,7 +5298,7 @@
         <v>0.1407998964001308</v>
       </c>
     </row>
-    <row r="59" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A59">
         <v>16</v>
       </c>
@@ -5333,7 +5333,7 @@
         <v>0.1432890331998351</v>
       </c>
     </row>
-    <row r="60" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A60">
         <v>16</v>
       </c>
@@ -5368,7 +5368,7 @@
         <v>0.13305474779772339</v>
       </c>
     </row>
-    <row r="61" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A61">
         <v>16</v>
       </c>
@@ -5403,7 +5403,7 @@
         <v>0.1301218176013208</v>
       </c>
     </row>
-    <row r="62" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A62">
         <v>16</v>
       </c>
@@ -5438,7 +5438,7 @@
         <v>0.14450794420117749</v>
       </c>
     </row>
-    <row r="63" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A63">
         <v>16</v>
       </c>
@@ -5473,7 +5473,7 @@
         <v>0.1313890785997501</v>
       </c>
     </row>
-    <row r="64" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A64">
         <v>16</v>
       </c>
@@ -5508,7 +5508,7 @@
         <v>0.12670726220094369</v>
       </c>
     </row>
-    <row r="65" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A65">
         <v>16</v>
       </c>
@@ -5543,7 +5543,7 @@
         <v>0.13942452640039851</v>
       </c>
     </row>
-    <row r="66" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A66">
         <v>16</v>
       </c>
@@ -5578,7 +5578,7 @@
         <v>0.14996077800024071</v>
       </c>
     </row>
-    <row r="67" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A67">
         <v>17</v>
       </c>
@@ -5613,7 +5613,7 @@
         <v>0.15018553840054669</v>
       </c>
     </row>
-    <row r="68" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A68">
         <v>17</v>
       </c>
@@ -5648,7 +5648,7 @@
         <v>0.13653221279964781</v>
       </c>
     </row>
-    <row r="69" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A69">
         <v>17</v>
       </c>
@@ -5683,7 +5683,7 @@
         <v>0.13838203400227941</v>
       </c>
     </row>
-    <row r="70" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A70">
         <v>17</v>
       </c>
@@ -5718,7 +5718,7 @@
         <v>0.1452009756001644</v>
       </c>
     </row>
-    <row r="71" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A71">
         <v>17</v>
       </c>
@@ -5753,7 +5753,7 @@
         <v>0.14833363340003419</v>
       </c>
     </row>
-    <row r="72" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A72">
         <v>17</v>
       </c>
@@ -5788,7 +5788,7 @@
         <v>0.14808649199985671</v>
       </c>
     </row>
-    <row r="73" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A73">
         <v>17</v>
       </c>
@@ -5823,7 +5823,7 @@
         <v>0.15395400279958271</v>
       </c>
     </row>
-    <row r="74" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A74">
         <v>17</v>
       </c>
@@ -5858,7 +5858,7 @@
         <v>0.1510180566008785</v>
       </c>
     </row>
-    <row r="75" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A75">
         <v>17</v>
       </c>
@@ -5893,7 +5893,7 @@
         <v>0.13643601420044429</v>
       </c>
     </row>
-    <row r="76" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A76">
         <v>17</v>
       </c>
@@ -5928,7 +5928,7 @@
         <v>0.15225932600005759</v>
       </c>
     </row>
-    <row r="77" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A77">
         <v>17</v>
       </c>
@@ -5963,7 +5963,7 @@
         <v>0.1482836359995417</v>
       </c>
     </row>
-    <row r="78" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A78">
         <v>17</v>
       </c>
@@ -5998,7 +5998,7 @@
         <v>0.1474866104006651</v>
       </c>
     </row>
-    <row r="79" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A79">
         <v>17</v>
       </c>
@@ -6033,7 +6033,7 @@
         <v>0.15536272580065999</v>
       </c>
     </row>
-    <row r="80" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A80">
         <v>17</v>
       </c>
@@ -6068,7 +6068,7 @@
         <v>0.1503598801995395</v>
       </c>
     </row>
-    <row r="81" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="81" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A81">
         <v>17</v>
       </c>
@@ -6103,7 +6103,7 @@
         <v>0.14109582420205699</v>
       </c>
     </row>
-    <row r="82" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="82" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A82">
         <v>17</v>
       </c>
@@ -6138,7 +6138,7 @@
         <v>0.14861841759848179</v>
       </c>
     </row>
-    <row r="83" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="83" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A83">
         <v>17</v>
       </c>
@@ -6173,7 +6173,7 @@
         <v>0.15091056440141981</v>
       </c>
     </row>
-    <row r="84" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="84" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A84">
         <v>17</v>
       </c>
@@ -6208,7 +6208,7 @@
         <v>0.1426887905996409</v>
       </c>
     </row>
-    <row r="85" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="85" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A85">
         <v>17</v>
       </c>
@@ -6243,7 +6243,7 @@
         <v>0.12732383639959149</v>
       </c>
     </row>
-    <row r="86" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="86" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A86">
         <v>17</v>
       </c>
@@ -6278,7 +6278,7 @@
         <v>0.14304621519986541</v>
       </c>
     </row>
-    <row r="87" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="87" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A87">
         <v>17</v>
       </c>
@@ -6313,7 +6313,7 @@
         <v>0.13362163600104399</v>
       </c>
     </row>
-    <row r="88" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="88" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A88">
         <v>17</v>
       </c>
@@ -6348,7 +6348,7 @@
         <v>0.13858108400017949</v>
       </c>
     </row>
-    <row r="89" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="89" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A89">
         <v>17</v>
       </c>
@@ -6383,7 +6383,7 @@
         <v>0.13446327519923221</v>
       </c>
     </row>
-    <row r="90" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="90" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A90">
         <v>17</v>
       </c>
@@ -6418,7 +6418,7 @@
         <v>0.13619524460082169</v>
       </c>
     </row>
-    <row r="91" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="91" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A91">
         <v>17</v>
       </c>
@@ -6453,7 +6453,7 @@
         <v>0.14228295599896229</v>
       </c>
     </row>
-    <row r="92" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="92" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A92">
         <v>17</v>
       </c>
@@ -6488,7 +6488,7 @@
         <v>0.14143252100038811</v>
       </c>
     </row>
-    <row r="93" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="93" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A93">
         <v>17</v>
       </c>
@@ -6523,7 +6523,7 @@
         <v>0.14540871339850131</v>
       </c>
     </row>
-    <row r="94" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="94" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A94">
         <v>17</v>
       </c>
@@ -6558,7 +6558,7 @@
         <v>0.14512626819923749</v>
       </c>
     </row>
-    <row r="95" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="95" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A95">
         <v>17</v>
       </c>
@@ -6593,7 +6593,7 @@
         <v>0.13966115119837921</v>
       </c>
     </row>
-    <row r="96" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="96" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A96">
         <v>17</v>
       </c>
@@ -6628,7 +6628,7 @@
         <v>0.14065134220290931</v>
       </c>
     </row>
-    <row r="97" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="97" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A97">
         <v>17</v>
       </c>
@@ -6663,7 +6663,7 @@
         <v>0.13836667259893151</v>
       </c>
     </row>
-    <row r="98" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="98" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A98">
         <v>17</v>
       </c>
@@ -6698,7 +6698,7 @@
         <v>0.1393414226011373</v>
       </c>
     </row>
-    <row r="99" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="99" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A99">
         <v>17</v>
       </c>
@@ -6733,7 +6733,7 @@
         <v>0.14245520360127559</v>
       </c>
     </row>
-    <row r="100" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="100" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A100">
         <v>17</v>
       </c>
@@ -6768,7 +6768,7 @@
         <v>0.14746884879859859</v>
       </c>
     </row>
-    <row r="101" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="101" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A101">
         <v>17</v>
       </c>
@@ -6803,7 +6803,7 @@
         <v>0.14168068760045571</v>
       </c>
     </row>
-    <row r="102" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="102" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A102">
         <v>17</v>
       </c>
@@ -6838,7 +6838,7 @@
         <v>0.14505279399891149</v>
       </c>
     </row>
-    <row r="103" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="103" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A103">
         <v>17</v>
       </c>
@@ -6873,7 +6873,7 @@
         <v>0.1370826136029791</v>
       </c>
     </row>
-    <row r="104" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="104" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A104">
         <v>17</v>
       </c>
@@ -6908,7 +6908,7 @@
         <v>0.13997599220019771</v>
       </c>
     </row>
-    <row r="105" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="105" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A105">
         <v>17</v>
       </c>
@@ -6943,7 +6943,7 @@
         <v>0.13886138539819509</v>
       </c>
     </row>
-    <row r="106" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="106" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A106">
         <v>17</v>
       </c>
@@ -6978,7 +6978,7 @@
         <v>0.1411169119965052</v>
       </c>
     </row>
-    <row r="107" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="107" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A107">
         <v>17</v>
       </c>
@@ -7013,7 +7013,7 @@
         <v>0.14101130219933111</v>
       </c>
     </row>
-    <row r="108" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="108" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A108">
         <v>17</v>
       </c>
@@ -7048,7 +7048,7 @@
         <v>0.1371948763990076</v>
       </c>
     </row>
-    <row r="109" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="109" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A109">
         <v>17</v>
       </c>
@@ -7083,7 +7083,7 @@
         <v>0.13732386359915841</v>
       </c>
     </row>
-    <row r="110" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="110" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A110">
         <v>17</v>
       </c>
@@ -7118,7 +7118,7 @@
         <v>0.1389807746003498</v>
       </c>
     </row>
-    <row r="111" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="111" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A111">
         <v>17</v>
       </c>
@@ -7153,7 +7153,7 @@
         <v>0.13962589519942409</v>
       </c>
     </row>
-    <row r="112" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="112" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A112">
         <v>17</v>
       </c>
@@ -7188,7 +7188,7 @@
         <v>0.13627013280056419</v>
       </c>
     </row>
-    <row r="113" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="113" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A113">
         <v>17</v>
       </c>
@@ -7223,7 +7223,7 @@
         <v>0.143328090198338</v>
       </c>
     </row>
-    <row r="114" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="114" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A114">
         <v>17</v>
       </c>
@@ -7258,7 +7258,7 @@
         <v>0.1328945790010039</v>
       </c>
     </row>
-    <row r="115" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="115" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A115">
         <v>17</v>
       </c>
@@ -7293,7 +7293,7 @@
         <v>0.14119635799870589</v>
       </c>
     </row>
-    <row r="116" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="116" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A116">
         <v>17</v>
       </c>
@@ -7328,7 +7328,7 @@
         <v>0.14397978019842411</v>
       </c>
     </row>
-    <row r="117" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="117" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A117">
         <v>17</v>
       </c>
@@ -7363,7 +7363,7 @@
         <v>0.1458327019994613</v>
       </c>
     </row>
-    <row r="118" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="118" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A118">
         <v>17</v>
       </c>
@@ -7398,7 +7398,7 @@
         <v>0.1422839796010521</v>
       </c>
     </row>
-    <row r="119" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="119" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A119">
         <v>17</v>
       </c>
@@ -7433,7 +7433,7 @@
         <v>0.14744893280003449</v>
       </c>
     </row>
-    <row r="120" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="120" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A120">
         <v>17</v>
       </c>
@@ -7468,7 +7468,7 @@
         <v>0.14325724360096501</v>
       </c>
     </row>
-    <row r="121" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="121" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A121">
         <v>17</v>
       </c>
@@ -7503,7 +7503,7 @@
         <v>0.15129867659852611</v>
       </c>
     </row>
-    <row r="122" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="122" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A122">
         <v>17</v>
       </c>
@@ -7538,7 +7538,7 @@
         <v>0.14293680680129911</v>
       </c>
     </row>
-    <row r="123" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="123" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A123">
         <v>17</v>
       </c>
@@ -7573,7 +7573,7 @@
         <v>0.1488105938013177</v>
       </c>
     </row>
-    <row r="124" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="124" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A124">
         <v>17</v>
       </c>
@@ -7608,7 +7608,7 @@
         <v>0.1456359549993067</v>
       </c>
     </row>
-    <row r="125" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="125" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A125">
         <v>17</v>
       </c>
@@ -7643,7 +7643,7 @@
         <v>0.14248004460241651</v>
       </c>
     </row>
-    <row r="126" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="126" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A126">
         <v>17</v>
       </c>
@@ -7678,7 +7678,7 @@
         <v>0.14500910079950699</v>
       </c>
     </row>
-    <row r="127" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="127" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A127">
         <v>17</v>
       </c>
@@ -7713,7 +7713,7 @@
         <v>0.14026315259980041</v>
       </c>
     </row>
-    <row r="128" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="128" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A128">
         <v>17</v>
       </c>
@@ -7748,7 +7748,7 @@
         <v>0.14506306959956419</v>
       </c>
     </row>
-    <row r="129" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="129" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A129">
         <v>17</v>
       </c>
@@ -7783,7 +7783,7 @@
         <v>0.14987243480136389</v>
       </c>
     </row>
-    <row r="130" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="130" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A130">
         <v>17</v>
       </c>
@@ -7818,7 +7818,7 @@
         <v>0.145196365598531</v>
       </c>
     </row>
-    <row r="131" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="131" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A131">
         <v>17</v>
       </c>
@@ -7853,7 +7853,7 @@
         <v>0.14707584800053161</v>
       </c>
     </row>
-    <row r="132" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="132" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A132">
         <v>17</v>
       </c>
@@ -7888,7 +7888,7 @@
         <v>0.15916911660024199</v>
       </c>
     </row>
-    <row r="133" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="133" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A133">
         <v>17</v>
       </c>
@@ -7923,7 +7923,7 @@
         <v>0.15154898900073019</v>
       </c>
     </row>
-    <row r="134" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="134" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A134">
         <v>17</v>
       </c>
@@ -7958,7 +7958,7 @@
         <v>0.15353067499818279</v>
       </c>
     </row>
-    <row r="135" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="135" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A135">
         <v>17</v>
       </c>
@@ -7993,7 +7993,7 @@
         <v>0.15051271800184621</v>
       </c>
     </row>
-    <row r="136" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="136" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A136">
         <v>17</v>
       </c>
@@ -8028,7 +8028,7 @@
         <v>0.15258653060009239</v>
       </c>
     </row>
-    <row r="137" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="137" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A137">
         <v>17</v>
       </c>
@@ -8063,7 +8063,7 @@
         <v>0.14861125479947079</v>
       </c>
     </row>
-    <row r="138" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="138" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A138">
         <v>17</v>
       </c>
@@ -8098,7 +8098,7 @@
         <v>0.147250429399719</v>
       </c>
     </row>
-    <row r="139" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="139" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A139">
         <v>17</v>
       </c>
@@ -8133,7 +8133,7 @@
         <v>0.1493974827986676</v>
       </c>
     </row>
-    <row r="140" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="140" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A140">
         <v>17</v>
       </c>
@@ -8168,7 +8168,7 @@
         <v>0.1582674068020424</v>
       </c>
     </row>
-    <row r="141" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="141" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A141">
         <v>17</v>
       </c>
@@ -8203,7 +8203,7 @@
         <v>0.15015317740180761</v>
       </c>
     </row>
-    <row r="142" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="142" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A142">
         <v>17</v>
       </c>
@@ -8238,7 +8238,7 @@
         <v>0.1532407120001153</v>
       </c>
     </row>
-    <row r="143" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="143" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A143">
         <v>17</v>
       </c>
@@ -8273,7 +8273,7 @@
         <v>0.15611890940053849</v>
       </c>
     </row>
-    <row r="144" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="144" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A144">
         <v>17</v>
       </c>
@@ -8308,7 +8308,7 @@
         <v>0.14849813000182621</v>
       </c>
     </row>
-    <row r="145" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="145" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A145">
         <v>17</v>
       </c>
@@ -8343,7 +8343,7 @@
         <v>0.15477695159934229</v>
       </c>
     </row>
-    <row r="146" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="146" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A146">
         <v>17</v>
       </c>
@@ -8378,7 +8378,7 @@
         <v>0.15435909759980859</v>
       </c>
     </row>
-    <row r="147" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="147" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A147">
         <v>17</v>
       </c>
@@ -8413,7 +8413,7 @@
         <v>0.15468619360035521</v>
       </c>
     </row>
-    <row r="148" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="148" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A148">
         <v>17</v>
       </c>
@@ -8448,7 +8448,7 @@
         <v>0.15094049920153341</v>
       </c>
     </row>
-    <row r="149" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="149" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A149">
         <v>17</v>
       </c>
@@ -8483,7 +8483,7 @@
         <v>0.1505537668024772</v>
       </c>
     </row>
-    <row r="150" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="150" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A150">
         <v>17</v>
       </c>
@@ -8518,7 +8518,7 @@
         <v>0.15738807400193761</v>
       </c>
     </row>
-    <row r="151" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="151" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A151">
         <v>17</v>
       </c>
@@ -8553,7 +8553,7 @@
         <v>0.15285351060156241</v>
       </c>
     </row>
-    <row r="152" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="152" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A152">
         <v>17</v>
       </c>
@@ -8588,7 +8588,7 @@
         <v>0.15639099580148469</v>
       </c>
     </row>
-    <row r="153" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="153" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A153">
         <v>17</v>
       </c>
@@ -8623,7 +8623,7 @@
         <v>0.1523481677984819</v>
       </c>
     </row>
-    <row r="154" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="154" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A154">
         <v>17</v>
       </c>
@@ -8658,7 +8658,7 @@
         <v>0.1682273597994936</v>
       </c>
     </row>
-    <row r="155" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="155" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A155">
         <v>17</v>
       </c>
@@ -8693,7 +8693,7 @@
         <v>0.1613241226004902</v>
       </c>
     </row>
-    <row r="156" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="156" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A156">
         <v>17</v>
       </c>
@@ -8728,7 +8728,7 @@
         <v>0.1590943825984141</v>
       </c>
     </row>
-    <row r="157" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="157" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A157">
         <v>17</v>
       </c>
@@ -8763,7 +8763,7 @@
         <v>0.15391489219910001</v>
       </c>
     </row>
-    <row r="158" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="158" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A158">
         <v>17</v>
       </c>
@@ -8798,7 +8798,7 @@
         <v>0.15060827320121459</v>
       </c>
     </row>
-    <row r="159" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="159" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A159">
         <v>17</v>
       </c>
@@ -8833,7 +8833,7 @@
         <v>0.16245988480077361</v>
       </c>
     </row>
-    <row r="160" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="160" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A160">
         <v>17</v>
       </c>
@@ -8868,7 +8868,7 @@
         <v>0.14934923879918641</v>
       </c>
     </row>
-    <row r="161" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="161" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A161">
         <v>17</v>
       </c>
@@ -8903,7 +8903,7 @@
         <v>0.15552832980029049</v>
       </c>
     </row>
-    <row r="162" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="162" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A162">
         <v>17</v>
       </c>
@@ -8938,7 +8938,7 @@
         <v>0.15434147419873631</v>
       </c>
     </row>
-    <row r="163" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="163" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A163">
         <v>18</v>
       </c>
@@ -8973,7 +8973,7 @@
         <v>0.15393692899815509</v>
       </c>
     </row>
-    <row r="164" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="164" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A164">
         <v>18</v>
       </c>
@@ -9008,7 +9008,7 @@
         <v>0.15744208059768419</v>
       </c>
     </row>
-    <row r="165" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="165" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A165">
         <v>18</v>
       </c>
@@ -9043,7 +9043,7 @@
         <v>0.15338003899814789</v>
       </c>
     </row>
-    <row r="166" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="166" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A166">
         <v>18</v>
       </c>
@@ -9078,7 +9078,7 @@
         <v>0.15375786620134019</v>
       </c>
     </row>
-    <row r="167" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="167" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A167">
         <v>18</v>
       </c>
@@ -9113,7 +9113,7 @@
         <v>0.15214955459960039</v>
       </c>
     </row>
-    <row r="168" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="168" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A168">
         <v>18</v>
       </c>
@@ -9148,7 +9148,7 @@
         <v>0.14773761659889709</v>
       </c>
     </row>
-    <row r="169" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="169" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A169">
         <v>18</v>
       </c>
@@ -9183,7 +9183,7 @@
         <v>0.14600249659997641</v>
       </c>
     </row>
-    <row r="170" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="170" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A170">
         <v>18</v>
       </c>
@@ -9218,7 +9218,7 @@
         <v>0.14969558679731559</v>
       </c>
     </row>
-    <row r="171" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="171" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A171">
         <v>18</v>
       </c>
@@ -9253,7 +9253,7 @@
         <v>0.15038243859889919</v>
       </c>
     </row>
-    <row r="172" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="172" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A172">
         <v>18</v>
       </c>
@@ -9288,7 +9288,7 @@
         <v>0.14948335659864831</v>
       </c>
     </row>
-    <row r="173" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="173" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A173">
         <v>18</v>
       </c>
@@ -9323,7 +9323,7 @@
         <v>0.15424226340110181</v>
       </c>
     </row>
-    <row r="174" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="174" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A174">
         <v>18</v>
       </c>
@@ -9358,7 +9358,7 @@
         <v>0.14910541299905161</v>
       </c>
     </row>
-    <row r="175" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="175" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A175">
         <v>18</v>
       </c>
@@ -9393,7 +9393,7 @@
         <v>0.15179938439978291</v>
       </c>
     </row>
-    <row r="176" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="176" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A176">
         <v>18</v>
       </c>
@@ -9428,7 +9428,7 @@
         <v>0.15347528220154341</v>
       </c>
     </row>
-    <row r="177" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="177" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A177">
         <v>18</v>
       </c>
@@ -9463,7 +9463,7 @@
         <v>0.15452180260181189</v>
       </c>
     </row>
-    <row r="178" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="178" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A178">
         <v>18</v>
       </c>
@@ -9498,7 +9498,7 @@
         <v>0.14847222519747449</v>
       </c>
     </row>
-    <row r="179" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="179" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A179">
         <v>18</v>
       </c>
@@ -9533,7 +9533,7 @@
         <v>0.16344014279893601</v>
       </c>
     </row>
-    <row r="180" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="180" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A180">
         <v>18</v>
       </c>
@@ -9568,7 +9568,7 @@
         <v>0.1513063902006252</v>
       </c>
     </row>
-    <row r="181" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="181" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A181">
         <v>18</v>
       </c>
@@ -9603,7 +9603,7 @@
         <v>0.1525459869997576</v>
       </c>
     </row>
-    <row r="182" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="182" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A182">
         <v>18</v>
       </c>
@@ -9638,7 +9638,7 @@
         <v>0.15214659160265001</v>
       </c>
     </row>
-    <row r="183" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="183" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A183">
         <v>18</v>
       </c>
@@ -9673,7 +9673,7 @@
         <v>0.15122415439982431</v>
       </c>
     </row>
-    <row r="184" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="184" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A184">
         <v>18</v>
       </c>
@@ -9708,7 +9708,7 @@
         <v>0.150989471799403</v>
       </c>
     </row>
-    <row r="185" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="185" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A185">
         <v>18</v>
       </c>
@@ -9743,7 +9743,7 @@
         <v>0.15670752780133629</v>
       </c>
     </row>
-    <row r="186" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="186" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A186">
         <v>18</v>
       </c>
@@ -9778,7 +9778,7 @@
         <v>0.15068381679884621</v>
       </c>
     </row>
-    <row r="187" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="187" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A187">
         <v>18</v>
       </c>
@@ -9813,7 +9813,7 @@
         <v>0.15548680100037021</v>
       </c>
     </row>
-    <row r="188" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="188" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A188">
         <v>18</v>
       </c>
@@ -9848,7 +9848,7 @@
         <v>0.15552517600153809</v>
       </c>
     </row>
-    <row r="189" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="189" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A189">
         <v>18</v>
       </c>
@@ -9883,7 +9883,7 @@
         <v>0.15075138739921379</v>
       </c>
     </row>
-    <row r="190" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="190" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A190">
         <v>18</v>
       </c>
@@ -9918,7 +9918,7 @@
         <v>0.15590662500180771</v>
       </c>
     </row>
-    <row r="191" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="191" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A191">
         <v>18</v>
       </c>
@@ -9953,7 +9953,7 @@
         <v>0.1527585377989453</v>
       </c>
     </row>
-    <row r="192" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="192" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A192">
         <v>18</v>
       </c>
@@ -9988,7 +9988,7 @@
         <v>0.159665779399802</v>
       </c>
     </row>
-    <row r="193" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="193" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A193">
         <v>18</v>
       </c>
@@ -10023,7 +10023,7 @@
         <v>0.15597195119917159</v>
       </c>
     </row>
-    <row r="194" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="194" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A194">
         <v>18</v>
       </c>
@@ -10058,7 +10058,7 @@
         <v>0.1482032368003274</v>
       </c>
     </row>
-    <row r="195" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="195" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A195">
         <v>18</v>
       </c>
@@ -10093,7 +10093,7 @@
         <v>0.15461904160038101</v>
       </c>
     </row>
-    <row r="196" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="196" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A196">
         <v>18</v>
       </c>
@@ -10128,7 +10128,7 @@
         <v>0.1508440643985523</v>
       </c>
     </row>
-    <row r="197" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="197" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A197">
         <v>18</v>
       </c>
@@ -10163,7 +10163,7 @@
         <v>0.16214703480072781</v>
       </c>
     </row>
-    <row r="198" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="198" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A198">
         <v>18</v>
       </c>
@@ -10198,7 +10198,7 @@
         <v>0.15754096460150319</v>
       </c>
     </row>
-    <row r="199" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="199" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A199">
         <v>18</v>
       </c>
@@ -10233,7 +10233,7 @@
         <v>0.1554064649986685</v>
       </c>
     </row>
-    <row r="200" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="200" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A200">
         <v>18</v>
       </c>
@@ -10268,7 +10268,7 @@
         <v>0.1471733693993883</v>
       </c>
     </row>
-    <row r="201" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="201" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A201">
         <v>18</v>
       </c>
@@ -10303,7 +10303,7 @@
         <v>0.1527722224011086</v>
       </c>
     </row>
-    <row r="202" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="202" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A202">
         <v>18</v>
       </c>
@@ -10338,7 +10338,7 @@
         <v>0.14917546659853539</v>
       </c>
     </row>
-    <row r="203" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="203" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A203">
         <v>18</v>
       </c>
@@ -10373,7 +10373,7 @@
         <v>0.14862012259836771</v>
       </c>
     </row>
-    <row r="204" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="204" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A204">
         <v>18</v>
       </c>
@@ -10408,7 +10408,7 @@
         <v>0.15527555719891101</v>
       </c>
     </row>
-    <row r="205" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="205" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A205">
         <v>18</v>
       </c>
@@ -10443,7 +10443,7 @@
         <v>0.15208377939852649</v>
       </c>
     </row>
-    <row r="206" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="206" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A206">
         <v>18</v>
       </c>
@@ -10478,7 +10478,7 @@
         <v>0.15957484459795521</v>
       </c>
     </row>
-    <row r="207" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="207" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A207">
         <v>18</v>
       </c>
@@ -10513,7 +10513,7 @@
         <v>0.155319297000824</v>
       </c>
     </row>
-    <row r="208" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="208" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A208">
         <v>18</v>
       </c>
@@ -10548,7 +10548,7 @@
         <v>0.1510131251998246</v>
       </c>
     </row>
-    <row r="209" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="209" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A209">
         <v>18</v>
       </c>
@@ -10583,7 +10583,7 @@
         <v>0.14878261019912309</v>
       </c>
     </row>
-    <row r="210" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="210" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A210">
         <v>18</v>
       </c>
@@ -10618,7 +10618,7 @@
         <v>0.15048861779941941</v>
       </c>
     </row>
-    <row r="211" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="211" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A211">
         <v>18</v>
       </c>
@@ -10653,7 +10653,7 @@
         <v>0.15584894960047679</v>
       </c>
     </row>
-    <row r="212" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="212" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A212">
         <v>18</v>
       </c>
@@ -10688,7 +10688,7 @@
         <v>0.15250056799850431</v>
       </c>
     </row>
-    <row r="213" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="213" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A213">
         <v>18</v>
       </c>
@@ -10723,7 +10723,7 @@
         <v>0.15721056660113389</v>
       </c>
     </row>
-    <row r="214" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="214" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A214">
         <v>18</v>
       </c>
@@ -10758,7 +10758,7 @@
         <v>0.15007800080347811</v>
       </c>
     </row>
-    <row r="215" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="215" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A215">
         <v>18</v>
       </c>
@@ -10793,7 +10793,7 @@
         <v>0.14998858619946989</v>
       </c>
     </row>
-    <row r="216" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="216" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A216">
         <v>18</v>
       </c>
@@ -10828,7 +10828,7 @@
         <v>0.15393010000116189</v>
       </c>
     </row>
-    <row r="217" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="217" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A217">
         <v>18</v>
       </c>
@@ -10863,7 +10863,7 @@
         <v>0.14726988919719591</v>
       </c>
     </row>
-    <row r="218" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="218" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A218">
         <v>18</v>
       </c>
@@ -10898,7 +10898,7 @@
         <v>0.15090097040083489</v>
       </c>
     </row>
-    <row r="219" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="219" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A219">
         <v>18</v>
       </c>
@@ -10933,7 +10933,7 @@
         <v>0.15146617139835139</v>
       </c>
     </row>
-    <row r="220" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="220" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A220">
         <v>18</v>
       </c>
@@ -10968,7 +10968,7 @@
         <v>0.14849130840302679</v>
       </c>
     </row>
-    <row r="221" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="221" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A221">
         <v>18</v>
       </c>
@@ -11003,7 +11003,7 @@
         <v>0.15346342300035759</v>
       </c>
     </row>
-    <row r="222" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="222" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A222">
         <v>18</v>
       </c>
@@ -11038,7 +11038,7 @@
         <v>0.14966587020171571</v>
       </c>
     </row>
-    <row r="223" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="223" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A223">
         <v>18</v>
       </c>
@@ -11073,7 +11073,7 @@
         <v>0.14624555300106301</v>
       </c>
     </row>
-    <row r="224" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="224" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A224">
         <v>18</v>
       </c>
@@ -11108,7 +11108,7 @@
         <v>0.15232396919891469</v>
       </c>
     </row>
-    <row r="225" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="225" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A225">
         <v>18</v>
       </c>
@@ -11143,7 +11143,7 @@
         <v>0.15088696420134509</v>
       </c>
     </row>
-    <row r="226" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="226" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A226">
         <v>18</v>
       </c>
@@ -11178,7 +11178,7 @@
         <v>0.14996262339846</v>
       </c>
     </row>
-    <row r="227" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="227" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A227">
         <v>18</v>
       </c>
@@ -11213,7 +11213,7 @@
         <v>0.14922201820008921</v>
       </c>
     </row>
-    <row r="228" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="228" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A228">
         <v>18</v>
       </c>
@@ -11248,7 +11248,7 @@
         <v>0.15752689880027901</v>
       </c>
     </row>
-    <row r="229" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="229" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A229">
         <v>18</v>
       </c>
@@ -11283,7 +11283,7 @@
         <v>0.14772074020002041</v>
       </c>
     </row>
-    <row r="230" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="230" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A230">
         <v>18</v>
       </c>
@@ -11318,7 +11318,7 @@
         <v>0.15158377400075551</v>
       </c>
     </row>
-    <row r="231" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="231" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A231">
         <v>18</v>
       </c>
@@ -11353,7 +11353,7 @@
         <v>0.15130001299985449</v>
       </c>
     </row>
-    <row r="232" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="232" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A232">
         <v>18</v>
       </c>
@@ -11388,7 +11388,7 @@
         <v>0.15261531259893671</v>
       </c>
     </row>
-    <row r="233" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="233" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A233">
         <v>18</v>
       </c>
@@ -11423,7 +11423,7 @@
         <v>0.15000597059988649</v>
       </c>
     </row>
-    <row r="234" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="234" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A234">
         <v>18</v>
       </c>
@@ -11458,7 +11458,7 @@
         <v>0.14746292299823829</v>
       </c>
     </row>
-    <row r="235" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="235" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A235">
         <v>18</v>
       </c>
@@ -11493,7 +11493,7 @@
         <v>0.15168059940187961</v>
       </c>
     </row>
-    <row r="236" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="236" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A236">
         <v>18</v>
       </c>
@@ -11528,7 +11528,7 @@
         <v>0.14826358740247089</v>
       </c>
     </row>
-    <row r="237" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="237" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A237">
         <v>18</v>
       </c>
@@ -11563,7 +11563,7 @@
         <v>0.1528333266003756</v>
       </c>
     </row>
-    <row r="238" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="238" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A238">
         <v>18</v>
       </c>
@@ -11598,7 +11598,7 @@
         <v>0.14758802359719991</v>
       </c>
     </row>
-    <row r="239" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="239" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A239">
         <v>18</v>
       </c>
@@ -11633,7 +11633,7 @@
         <v>0.15482421240158151</v>
       </c>
     </row>
-    <row r="240" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="240" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A240">
         <v>18</v>
       </c>
@@ -11668,7 +11668,7 @@
         <v>0.14704637579852711</v>
       </c>
     </row>
-    <row r="241" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="241" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A241">
         <v>18</v>
       </c>
@@ -11703,7 +11703,7 @@
         <v>0.1511510654003359</v>
       </c>
     </row>
-    <row r="242" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="242" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A242">
         <v>18</v>
       </c>
@@ -11738,7 +11738,7 @@
         <v>0.15131453560024971</v>
       </c>
     </row>
-    <row r="243" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="243" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A243">
         <v>18</v>
       </c>
@@ -11773,7 +11773,7 @@
         <v>0.15302216519776271</v>
       </c>
     </row>
-    <row r="244" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="244" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A244">
         <v>18</v>
       </c>
@@ -11808,7 +11808,7 @@
         <v>0.15209209060121789</v>
       </c>
     </row>
-    <row r="245" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="245" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A245">
         <v>18</v>
       </c>
@@ -11843,7 +11843,7 @@
         <v>0.1552104947986663</v>
       </c>
     </row>
-    <row r="246" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="246" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A246">
         <v>18</v>
       </c>
@@ -11878,7 +11878,7 @@
         <v>0.1514028535981197</v>
       </c>
     </row>
-    <row r="247" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="247" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A247">
         <v>18</v>
       </c>
@@ -11913,7 +11913,7 @@
         <v>0.1532233125981293</v>
       </c>
     </row>
-    <row r="248" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="248" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A248">
         <v>18</v>
       </c>
@@ -11948,7 +11948,7 @@
         <v>0.15072586260066601</v>
       </c>
     </row>
-    <row r="249" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="249" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A249">
         <v>18</v>
       </c>
@@ -11983,7 +11983,7 @@
         <v>0.14976849039812809</v>
       </c>
     </row>
-    <row r="250" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="250" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A250">
         <v>18</v>
       </c>
@@ -12018,7 +12018,7 @@
         <v>0.1431317581998883</v>
       </c>
     </row>
-    <row r="251" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="251" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A251">
         <v>18</v>
       </c>
@@ -12053,7 +12053,7 @@
         <v>0.14902650879957949</v>
       </c>
     </row>
-    <row r="252" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="252" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A252">
         <v>18</v>
       </c>
@@ -12088,7 +12088,7 @@
         <v>0.14999397020001201</v>
       </c>
     </row>
-    <row r="253" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="253" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A253">
         <v>18</v>
       </c>
@@ -12123,7 +12123,7 @@
         <v>0.14929165119974641</v>
       </c>
     </row>
-    <row r="254" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="254" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A254">
         <v>18</v>
       </c>
@@ -12158,7 +12158,7 @@
         <v>0.1476427799992962</v>
       </c>
     </row>
-    <row r="255" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="255" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A255">
         <v>18</v>
       </c>
@@ -12193,7 +12193,7 @@
         <v>0.14453622539876959</v>
       </c>
     </row>
-    <row r="256" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="256" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A256">
         <v>18</v>
       </c>
@@ -12228,7 +12228,7 @@
         <v>0.1429663224014803</v>
       </c>
     </row>
-    <row r="257" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="257" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A257">
         <v>18</v>
       </c>
@@ -12263,7 +12263,7 @@
         <v>0.1389701198015246</v>
       </c>
     </row>
-    <row r="258" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="258" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A258">
         <v>18</v>
       </c>
@@ -12298,7 +12298,7 @@
         <v>0.14002864439971749</v>
       </c>
     </row>
-    <row r="259" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="259" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A259">
         <v>19</v>
       </c>
@@ -12333,7 +12333,7 @@
         <v>1.483779580012197E-2</v>
       </c>
     </row>
-    <row r="260" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="260" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A260">
         <v>19</v>
       </c>
@@ -12368,7 +12368,7 @@
         <v>1.6851649200543758E-2</v>
       </c>
     </row>
-    <row r="261" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="261" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A261">
         <v>19</v>
       </c>
@@ -12403,7 +12403,7 @@
         <v>1.4084920599998441E-2</v>
       </c>
     </row>
-    <row r="262" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="262" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A262">
         <v>19</v>
       </c>
@@ -12438,7 +12438,7 @@
         <v>1.423688359936932E-2</v>
       </c>
     </row>
-    <row r="263" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="263" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A263">
         <v>19</v>
       </c>
@@ -12473,7 +12473,7 @@
         <v>1.4714948399341669E-2</v>
       </c>
     </row>
-    <row r="264" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="264" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A264">
         <v>19</v>
       </c>
@@ -12508,7 +12508,7 @@
         <v>1.541840940044494E-2</v>
       </c>
     </row>
-    <row r="265" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="265" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A265">
         <v>19</v>
       </c>
@@ -12543,7 +12543,7 @@
         <v>1.275095000164583E-2</v>
       </c>
     </row>
-    <row r="266" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="266" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A266">
         <v>19</v>
       </c>
@@ -12578,7 +12578,7 @@
         <v>1.5718081801605881E-2</v>
       </c>
     </row>
-    <row r="267" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="267" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A267">
         <v>19</v>
       </c>
@@ -12613,7 +12613,7 @@
         <v>1.367938080220483E-2</v>
       </c>
     </row>
-    <row r="268" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="268" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A268">
         <v>19</v>
       </c>
@@ -12648,7 +12648,7 @@
         <v>1.5475393402448389E-2</v>
       </c>
     </row>
-    <row r="269" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="269" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A269">
         <v>19</v>
       </c>
@@ -12683,7 +12683,7 @@
         <v>1.4863607198640241E-2</v>
       </c>
     </row>
-    <row r="270" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="270" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A270">
         <v>19</v>
       </c>
@@ -12718,7 +12718,7 @@
         <v>1.521877180057345E-2</v>
       </c>
     </row>
-    <row r="271" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="271" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A271">
         <v>19</v>
       </c>
@@ -12753,7 +12753,7 @@
         <v>1.4525011801742951E-2</v>
       </c>
     </row>
-    <row r="272" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="272" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A272">
         <v>19</v>
       </c>
@@ -12788,7 +12788,7 @@
         <v>1.5558418800355869E-2</v>
       </c>
     </row>
-    <row r="273" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="273" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A273">
         <v>19</v>
       </c>
@@ -12823,7 +12823,7 @@
         <v>1.380175439844606E-2</v>
       </c>
     </row>
-    <row r="274" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="274" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A274">
         <v>19</v>
       </c>
@@ -12858,7 +12858,7 @@
         <v>1.3218074398173491E-2</v>
       </c>
     </row>
-    <row r="275" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="275" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A275">
         <v>19</v>
       </c>
@@ -12893,7 +12893,7 @@
         <v>1.5573635598411781E-2</v>
       </c>
     </row>
-    <row r="276" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="276" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A276">
         <v>19</v>
       </c>
@@ -12928,7 +12928,7 @@
         <v>1.4175731599971189E-2</v>
       </c>
     </row>
-    <row r="277" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="277" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A277">
         <v>19</v>
       </c>
@@ -12963,7 +12963,7 @@
         <v>1.449008920317283E-2</v>
       </c>
     </row>
-    <row r="278" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="278" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A278">
         <v>19</v>
       </c>
@@ -12998,7 +12998,7 @@
         <v>1.4073153799108701E-2</v>
       </c>
     </row>
-    <row r="279" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="279" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A279">
         <v>19</v>
       </c>
@@ -13033,7 +13033,7 @@
         <v>1.5010969601280519E-2</v>
       </c>
     </row>
-    <row r="280" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="280" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A280">
         <v>19</v>
       </c>
@@ -13068,7 +13068,7 @@
         <v>1.4980514596390999E-2</v>
       </c>
     </row>
-    <row r="281" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="281" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A281">
         <v>19</v>
       </c>
@@ -13103,7 +13103,7 @@
         <v>1.53787668023142E-2</v>
       </c>
     </row>
-    <row r="282" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="282" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A282">
         <v>19</v>
       </c>
@@ -13138,7 +13138,7 @@
         <v>1.425987979891943E-2</v>
       </c>
     </row>
-    <row r="283" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="283" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A283">
         <v>19</v>
       </c>
@@ -13173,7 +13173,7 @@
         <v>1.310916499933228E-2</v>
       </c>
     </row>
-    <row r="284" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="284" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A284">
         <v>19</v>
       </c>
@@ -13208,7 +13208,7 @@
         <v>1.527969679882517E-2</v>
       </c>
     </row>
-    <row r="285" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="285" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A285">
         <v>19</v>
       </c>
@@ -13243,7 +13243,7 @@
         <v>1.392845479858806E-2</v>
       </c>
     </row>
-    <row r="286" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="286" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A286">
         <v>19</v>
       </c>
@@ -13278,7 +13278,7 @@
         <v>1.5801261000160591E-2</v>
       </c>
     </row>
-    <row r="287" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="287" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A287">
         <v>19</v>
       </c>
@@ -13313,7 +13313,7 @@
         <v>1.4486971199221439E-2</v>
       </c>
     </row>
-    <row r="288" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="288" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A288">
         <v>19</v>
       </c>
@@ -13348,7 +13348,7 @@
         <v>1.477902879996691E-2</v>
       </c>
     </row>
-    <row r="289" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="289" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A289">
         <v>19</v>
       </c>
@@ -13383,7 +13383,7 @@
         <v>1.6300975001649929E-2</v>
       </c>
     </row>
-    <row r="290" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="290" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A290">
         <v>19</v>
       </c>
@@ -13418,7 +13418,7 @@
         <v>1.455067840142874E-2</v>
       </c>
     </row>
-    <row r="291" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="291" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A291">
         <v>1</v>
       </c>
@@ -13453,7 +13453,7 @@
         <v>9.0068599965889009E-4</v>
       </c>
     </row>
-    <row r="292" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="292" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A292">
         <v>1</v>
       </c>
@@ -13488,7 +13488,7 @@
         <v>7.7642339747399094E-4</v>
       </c>
     </row>
-    <row r="293" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="293" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A293">
         <v>1</v>
       </c>
@@ -13523,7 +13523,7 @@
         <v>8.7996299989754332E-4</v>
       </c>
     </row>
-    <row r="294" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="294" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A294">
         <v>1</v>
       </c>
@@ -13558,7 +13558,7 @@
         <v>8.9155519963242109E-4</v>
       </c>
     </row>
-    <row r="295" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="295" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A295">
         <v>1</v>
       </c>
@@ -13593,7 +13593,7 @@
         <v>9.0748479997273537E-4</v>
       </c>
     </row>
-    <row r="296" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="296" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A296">
         <v>1</v>
       </c>
@@ -13628,7 +13628,7 @@
         <v>8.8016980007523673E-4</v>
       </c>
     </row>
-    <row r="297" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="297" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A297">
         <v>1</v>
       </c>
@@ -13663,7 +13663,7 @@
         <v>8.925369998905808E-4</v>
       </c>
     </row>
-    <row r="298" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="298" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A298">
         <v>1</v>
       </c>
@@ -13698,7 +13698,7 @@
         <v>8.6610319995088507E-4</v>
       </c>
     </row>
-    <row r="299" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="299" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A299">
         <v>1</v>
       </c>
@@ -13733,7 +13733,7 @@
         <v>9.378880000440404E-4</v>
       </c>
     </row>
-    <row r="300" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="300" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A300">
         <v>1</v>
       </c>
@@ -13768,7 +13768,7 @@
         <v>8.9293979981448497E-4</v>
       </c>
     </row>
-    <row r="301" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="301" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A301">
         <v>1</v>
       </c>
@@ -13803,7 +13803,7 @@
         <v>8.5716239991597833E-4</v>
       </c>
     </row>
-    <row r="302" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="302" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A302">
         <v>1</v>
       </c>
@@ -13838,7 +13838,7 @@
         <v>8.7614380172453823E-4</v>
       </c>
     </row>
-    <row r="303" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="303" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A303">
         <v>1</v>
       </c>
@@ -13873,7 +13873,7 @@
         <v>8.3558820188045502E-4</v>
       </c>
     </row>
-    <row r="304" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="304" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A304">
         <v>1</v>
       </c>
@@ -13908,7 +13908,7 @@
         <v>8.7479560170322657E-4</v>
       </c>
     </row>
-    <row r="305" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="305" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A305">
         <v>1</v>
       </c>
@@ -13943,7 +13943,7 @@
         <v>8.7770340032875536E-4</v>
       </c>
     </row>
-    <row r="306" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="306" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A306">
         <v>1</v>
       </c>
@@ -13978,7 +13978,7 @@
         <v>8.936268000979908E-4</v>
       </c>
     </row>
-    <row r="307" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="307" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A307">
         <v>2</v>
       </c>
@@ -14013,7 +14013,7 @@
         <v>2.6920234013232398E-3</v>
       </c>
     </row>
-    <row r="308" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="308" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A308">
         <v>2</v>
       </c>
@@ -14048,7 +14048,7 @@
         <v>2.1083175990497692E-3</v>
       </c>
     </row>
-    <row r="309" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="309" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A309">
         <v>2</v>
       </c>
@@ -14083,7 +14083,7 @@
         <v>2.4092694002320059E-3</v>
       </c>
     </row>
-    <row r="310" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="310" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A310">
         <v>2</v>
       </c>
@@ -14118,7 +14118,7 @@
         <v>2.6661589989089409E-3</v>
       </c>
     </row>
-    <row r="311" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="311" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A311">
         <v>2</v>
       </c>
@@ -14153,7 +14153,7 @@
         <v>2.4470042015309452E-3</v>
       </c>
     </row>
-    <row r="312" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="312" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A312">
         <v>2</v>
       </c>
@@ -14188,7 +14188,7 @@
         <v>2.4260168007458559E-3</v>
       </c>
     </row>
-    <row r="313" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="313" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A313">
         <v>2</v>
       </c>
@@ -14223,7 +14223,7 @@
         <v>2.337472999352031E-3</v>
       </c>
     </row>
-    <row r="314" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="314" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A314">
         <v>2</v>
       </c>
@@ -14258,7 +14258,7 @@
         <v>2.3691443988354882E-3</v>
       </c>
     </row>
-    <row r="315" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="315" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A315">
         <v>2</v>
       </c>
@@ -14293,7 +14293,7 @@
         <v>2.5309675984317441E-3</v>
       </c>
     </row>
-    <row r="316" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="316" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A316">
         <v>2</v>
       </c>
@@ -14328,7 +14328,7 @@
         <v>2.4059831994236451E-3</v>
       </c>
     </row>
-    <row r="317" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="317" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A317">
         <v>2</v>
       </c>
@@ -14363,7 +14363,7 @@
         <v>2.2288355990895069E-3</v>
       </c>
     </row>
-    <row r="318" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="318" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A318">
         <v>2</v>
       </c>
@@ -14398,7 +14398,7 @@
         <v>2.3181227996246891E-3</v>
       </c>
     </row>
-    <row r="319" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="319" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A319">
         <v>2</v>
       </c>
@@ -14433,7 +14433,7 @@
         <v>2.4967258010292421E-3</v>
       </c>
     </row>
-    <row r="320" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="320" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A320">
         <v>2</v>
       </c>
@@ -14468,7 +14468,7 @@
         <v>2.0044390010298231E-3</v>
       </c>
     </row>
-    <row r="321" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="321" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A321">
         <v>2</v>
       </c>
@@ -14503,7 +14503,7 @@
         <v>2.3268874007044359E-3</v>
       </c>
     </row>
-    <row r="322" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="322" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A322">
         <v>2</v>
       </c>
@@ -14538,7 +14538,7 @@
         <v>2.1264036011416471E-3</v>
       </c>
     </row>
-    <row r="323" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="323" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A323">
         <v>3</v>
       </c>
@@ -14573,7 +14573,7 @@
         <v>5.736682201677468E-3</v>
       </c>
     </row>
-    <row r="324" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="324" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A324">
         <v>3</v>
       </c>
@@ -14608,7 +14608,7 @@
         <v>5.2672061981866138E-3</v>
       </c>
     </row>
-    <row r="325" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="325" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A325">
         <v>3</v>
       </c>
@@ -14643,7 +14643,7 @@
         <v>5.2139239996904507E-3</v>
       </c>
     </row>
-    <row r="326" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="326" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A326">
         <v>3</v>
       </c>
@@ -14678,7 +14678,7 @@
         <v>6.3205219994415529E-3</v>
       </c>
     </row>
-    <row r="327" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="327" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A327">
         <v>3</v>
       </c>
@@ -14713,7 +14713,7 @@
         <v>4.8884099975111898E-3</v>
       </c>
     </row>
-    <row r="328" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="328" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A328">
         <v>3</v>
       </c>
@@ -14748,7 +14748,7 @@
         <v>5.7912244010367431E-3</v>
       </c>
     </row>
-    <row r="329" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="329" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A329">
         <v>3</v>
       </c>
@@ -14783,7 +14783,7 @@
         <v>5.960934198810719E-3</v>
       </c>
     </row>
-    <row r="330" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="330" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A330">
         <v>3</v>
       </c>
@@ -14818,7 +14818,7 @@
         <v>6.3276518005295646E-3</v>
       </c>
     </row>
-    <row r="331" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="331" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A331">
         <v>3</v>
       </c>
@@ -14853,7 +14853,7 @@
         <v>4.9858546000905333E-3</v>
       </c>
     </row>
-    <row r="332" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="332" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A332">
         <v>3</v>
       </c>
@@ -14888,7 +14888,7 @@
         <v>5.4324080003425477E-3</v>
       </c>
     </row>
-    <row r="333" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="333" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A333">
         <v>3</v>
       </c>
@@ -14923,7 +14923,7 @@
         <v>6.8258173996582627E-3</v>
       </c>
     </row>
-    <row r="334" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="334" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A334">
         <v>3</v>
       </c>
@@ -14958,7 +14958,7 @@
         <v>6.445690795953851E-3</v>
       </c>
     </row>
-    <row r="335" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="335" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A335">
         <v>3</v>
       </c>
@@ -14993,7 +14993,7 @@
         <v>5.7340927975019444E-3</v>
       </c>
     </row>
-    <row r="336" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="336" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A336">
         <v>3</v>
       </c>
@@ -15028,7 +15028,7 @@
         <v>6.1676534009166058E-3</v>
       </c>
     </row>
-    <row r="337" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="337" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A337">
         <v>3</v>
       </c>
@@ -15063,7 +15063,7 @@
         <v>5.6480379993445236E-3</v>
       </c>
     </row>
-    <row r="338" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="338" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A338">
         <v>3</v>
       </c>
@@ -15098,7 +15098,7 @@
         <v>5.2901312010362744E-3</v>
       </c>
     </row>
-    <row r="339" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="339" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A339">
         <v>3</v>
       </c>
@@ -15133,7 +15133,7 @@
         <v>5.5514125997433439E-3</v>
       </c>
     </row>
-    <row r="340" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="340" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A340">
         <v>3</v>
       </c>
@@ -15168,7 +15168,7 @@
         <v>6.1733903974527486E-3</v>
       </c>
     </row>
-    <row r="341" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="341" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A341">
         <v>3</v>
       </c>
@@ -15203,7 +15203,7 @@
         <v>5.6941920003737321E-3</v>
       </c>
     </row>
-    <row r="342" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="342" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A342">
         <v>3</v>
       </c>
@@ -15238,7 +15238,7 @@
         <v>5.8520522012258883E-3</v>
       </c>
     </row>
-    <row r="343" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="343" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A343">
         <v>3</v>
       </c>
@@ -15273,7 +15273,7 @@
         <v>5.4008844017516822E-3</v>
       </c>
     </row>
-    <row r="344" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="344" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A344">
         <v>3</v>
       </c>
@@ -15308,7 +15308,7 @@
         <v>5.8162550005363299E-3</v>
       </c>
     </row>
-    <row r="345" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="345" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A345">
         <v>3</v>
       </c>
@@ -15343,7 +15343,7 @@
         <v>6.0761606029700486E-3</v>
       </c>
     </row>
-    <row r="346" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="346" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A346">
         <v>3</v>
       </c>
@@ -15378,7 +15378,7 @@
         <v>5.3106774008483629E-3</v>
       </c>
     </row>
-    <row r="347" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="347" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A347">
         <v>3</v>
       </c>
@@ -15413,7 +15413,7 @@
         <v>6.3061730004847051E-3</v>
       </c>
     </row>
-    <row r="348" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="348" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A348">
         <v>3</v>
       </c>
@@ -15448,7 +15448,7 @@
         <v>5.9359374019550158E-3</v>
       </c>
     </row>
-    <row r="349" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="349" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A349">
         <v>3</v>
       </c>
@@ -15483,7 +15483,7 @@
         <v>5.2835908005363311E-3</v>
       </c>
     </row>
-    <row r="350" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="350" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A350">
         <v>3</v>
       </c>
@@ -15518,7 +15518,7 @@
         <v>5.0189205998321992E-3</v>
       </c>
     </row>
-    <row r="351" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="351" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A351">
         <v>3</v>
       </c>
@@ -15553,7 +15553,7 @@
         <v>5.8167177994619124E-3</v>
       </c>
     </row>
-    <row r="352" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="352" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A352">
         <v>3</v>
       </c>
@@ -15588,7 +15588,7 @@
         <v>6.3150838002911771E-3</v>
       </c>
     </row>
-    <row r="353" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="353" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A353">
         <v>3</v>
       </c>
@@ -15623,7 +15623,7 @@
         <v>6.1088173999451099E-3</v>
       </c>
     </row>
-    <row r="354" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="354" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A354">
         <v>3</v>
       </c>
@@ -15658,7 +15658,7 @@
         <v>6.527357800223399E-3</v>
       </c>
     </row>
-    <row r="355" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="355" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A355">
         <v>3</v>
       </c>
@@ -15693,7 +15693,7 @@
         <v>2.0074966014362872E-3</v>
       </c>
     </row>
-    <row r="356" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="356" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A356">
         <v>3</v>
       </c>
@@ -15728,7 +15728,7 @@
         <v>2.1022521992563269E-3</v>
       </c>
     </row>
-    <row r="357" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="357" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A357">
         <v>3</v>
       </c>
@@ -15763,7 +15763,7 @@
         <v>1.886181200097781E-3</v>
       </c>
     </row>
-    <row r="358" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="358" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A358">
         <v>3</v>
       </c>
@@ -15798,7 +15798,7 @@
         <v>2.2327429993310938E-3</v>
       </c>
     </row>
-    <row r="359" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="359" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A359">
         <v>3</v>
       </c>
@@ -15833,7 +15833,7 @@
         <v>2.238741799374111E-3</v>
       </c>
     </row>
-    <row r="360" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="360" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A360">
         <v>3</v>
       </c>
@@ -15868,7 +15868,7 @@
         <v>2.000980198499746E-3</v>
       </c>
     </row>
-    <row r="361" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="361" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A361">
         <v>3</v>
       </c>
@@ -15903,7 +15903,7 @@
         <v>2.2314583999104801E-3</v>
       </c>
     </row>
-    <row r="362" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="362" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A362">
         <v>3</v>
       </c>
@@ -15938,7 +15938,7 @@
         <v>2.0272135981940658E-3</v>
       </c>
     </row>
-    <row r="363" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="363" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A363">
         <v>3</v>
       </c>
@@ -15973,7 +15973,7 @@
         <v>1.908884401200339E-3</v>
       </c>
     </row>
-    <row r="364" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="364" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A364">
         <v>3</v>
       </c>
@@ -16008,7 +16008,7 @@
         <v>2.1016669998061839E-3</v>
       </c>
     </row>
-    <row r="365" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="365" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A365">
         <v>3</v>
       </c>
@@ -16043,7 +16043,7 @@
         <v>2.2856918003526521E-3</v>
       </c>
     </row>
-    <row r="366" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="366" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A366">
         <v>3</v>
       </c>
@@ -16078,7 +16078,7 @@
         <v>1.8699795997235921E-3</v>
       </c>
     </row>
-    <row r="367" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="367" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A367">
         <v>3</v>
       </c>
@@ -16113,7 +16113,7 @@
         <v>2.1361182007240131E-3</v>
       </c>
     </row>
-    <row r="368" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="368" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A368">
         <v>3</v>
       </c>
@@ -16148,7 +16148,7 @@
         <v>1.760905198170803E-3</v>
       </c>
     </row>
-    <row r="369" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="369" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A369">
         <v>3</v>
       </c>
@@ -16183,7 +16183,7 @@
         <v>2.1259193992591461E-3</v>
       </c>
     </row>
-    <row r="370" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="370" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A370">
         <v>3</v>
       </c>
@@ -16218,7 +16218,7 @@
         <v>1.9153379980707539E-3</v>
       </c>
     </row>
-    <row r="371" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="371" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A371">
         <v>3</v>
       </c>
@@ -16253,7 +16253,7 @@
         <v>1.9882695996784609E-3</v>
       </c>
     </row>
-    <row r="372" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="372" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A372">
         <v>3</v>
       </c>
@@ -16288,7 +16288,7 @@
         <v>1.826408199849538E-3</v>
       </c>
     </row>
-    <row r="373" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="373" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A373">
         <v>3</v>
       </c>
@@ -16323,7 +16323,7 @@
         <v>1.806176202080678E-3</v>
       </c>
     </row>
-    <row r="374" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="374" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A374">
         <v>3</v>
       </c>
@@ -16358,7 +16358,7 @@
         <v>2.260721600032412E-3</v>
       </c>
     </row>
-    <row r="375" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="375" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A375">
         <v>3</v>
       </c>
@@ -16393,7 +16393,7 @@
         <v>1.813660399056971E-3</v>
       </c>
     </row>
-    <row r="376" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="376" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A376">
         <v>3</v>
       </c>
@@ -16428,7 +16428,7 @@
         <v>1.780181998037733E-3</v>
       </c>
     </row>
-    <row r="377" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="377" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A377">
         <v>3</v>
       </c>
@@ -16463,7 +16463,7 @@
         <v>2.100051398156211E-3</v>
       </c>
     </row>
-    <row r="378" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="378" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A378">
         <v>3</v>
       </c>
@@ -16498,7 +16498,7 @@
         <v>1.889806402323302E-3</v>
       </c>
     </row>
-    <row r="381" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="381" spans="1:11" x14ac:dyDescent="0.45">
       <c r="F381" s="2" t="s">
         <v>379</v>
       </c>
@@ -16518,7 +16518,7 @@
         <v>387</v>
       </c>
     </row>
-    <row r="382" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="382" spans="1:11" x14ac:dyDescent="0.45">
       <c r="E382" s="3" t="s">
         <v>384</v>
       </c>
@@ -16547,7 +16547,7 @@
         <v>6.418027451823273E-2</v>
       </c>
     </row>
-    <row r="383" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="383" spans="1:11" x14ac:dyDescent="0.45">
       <c r="E383" s="3" t="s">
         <v>385</v>
       </c>
